--- a/S4 - Vendor Master_Obervations.xlsx
+++ b/S4 - Vendor Master_Obervations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ciplaltd-my.sharepoint.com/personal/pratima_shetye_cipla_com/Documents/Desktop/Vendor Mngmt/S4 HANA Testing/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC10489E795C43B25BDE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFA96780-C4B5-4C83-8942-878BDB518C70}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_F25DC773A252ABDACC10489E795C43B25BDE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{342E4FBC-3AA3-43ED-8854-228E4B8534AD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="358">
   <si>
     <t>Field Technical Name</t>
   </si>
@@ -467,9 +467,6 @@
     <t>durban</t>
   </si>
   <si>
-    <t>KN</t>
-  </si>
-  <si>
     <t>190948766</t>
   </si>
   <si>
@@ -494,9 +491,6 @@
     <t>EW</t>
   </si>
   <si>
-    <t>RMB01</t>
-  </si>
-  <si>
     <t>ZAR</t>
   </si>
   <si>
@@ -545,9 +539,6 @@
     <t>Y000</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>GBP</t>
   </si>
   <si>
@@ -563,9 +554,6 @@
     <t>Bowling Green,</t>
   </si>
   <si>
-    <t>432092</t>
-  </si>
-  <si>
     <t>Bowling Green</t>
   </si>
   <si>
@@ -686,15 +674,6 @@
     <t>99</t>
   </si>
   <si>
-    <t>Test run</t>
-  </si>
-  <si>
-    <t>Note : Purchase Org is not applicable to Emplyee code</t>
-  </si>
-  <si>
-    <t>Block / Unblocked - Successfully posted with error of Pur org for Employee code</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -1083,6 +1062,51 @@
   </si>
   <si>
     <t>ZP</t>
+  </si>
+  <si>
+    <t>ZN</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>43292</t>
+  </si>
+  <si>
+    <t>1120002</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>JI</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFB error while uploading TDS </t>
+  </si>
+  <si>
+    <t>Uploaded sucessfully</t>
+  </si>
+  <si>
+    <t>BP created successfully</t>
+  </si>
+  <si>
+    <t>Vendor extended successfully</t>
+  </si>
+  <si>
+    <t>Uploaded with error - 100170831 - SPERQ - can not be blank in case if Vendor Total block, same details updated successfully for another code</t>
+  </si>
+  <si>
+    <t>TAN details uploaded successfully</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1156,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1151,8 +1175,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1188,13 +1218,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1241,6 +1295,25 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1322,17 +1395,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2118426</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>174701</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>553735</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>21166</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41DEE90-82DD-4B25-AD41-4C2BF4F5F344}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{799F7EDD-28A9-BEB7-2E4B-42D05755CE91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1348,8 +1421,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1003300" y="1841500"/>
-          <a:ext cx="5020376" cy="543001"/>
+          <a:off x="1005417" y="1852083"/>
+          <a:ext cx="8406568" cy="2428875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1417,21 +1490,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>382095</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>51013</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E845141-D10A-4F7B-93E4-FC68F160091F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4618E95-7419-2A86-96DC-1B66838AF808}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1439,17 +1512,16 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect r="31553" b="61909"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="736600"/>
-          <a:ext cx="12515850" cy="3917950"/>
+          <a:off x="609600" y="920750"/>
+          <a:ext cx="7849695" cy="1524213"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1515,160 +1587,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>539750</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123926</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BB22317-8E8A-4095-B3D3-AA6495055563}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="1104900"/>
-          <a:ext cx="10369550" cy="1412976"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>393600</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>37720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>311400</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>139960</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="3" name="Ink 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10CFC91D-0FB0-43D4-B336-7B935F47F650}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="5956200" y="1510920"/>
-            <a:ext cx="4185000" cy="102240"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="4" name="Ink 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8665D0BE-8837-4522-E969-785DBE1B1168}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5902200" y="1402920"/>
-              <a:ext cx="4292640" cy="317880"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>150630</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D08131F-A3A3-43A8-9945-7356C5AB711D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:srcRect r="7170" b="7342"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609601" y="3683001"/>
-          <a:ext cx="10731499" cy="2176279"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>317160</xdr:colOff>
       <xdr:row>26</xdr:row>
@@ -1680,9 +1598,9 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>45010</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
               <a:extLst>
@@ -1700,7 +1618,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -1734,67 +1652,46 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476040</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>183710</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476400</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>184070</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>271277</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>120651</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="6" name="Ink 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE7B8BA2-A123-4AA8-8574-9FE40FED140B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="6038640" y="3130110"/>
-            <a:ext cx="360" cy="360"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="6" name="Ink 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE7B8BA2-A123-4AA8-8574-9FE40FED140B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5984640" y="3022470"/>
-              <a:ext cx="108000" cy="216000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B725C05D-E867-0AC3-B06A-4B8C00EEA7E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609601" y="1104901"/>
+          <a:ext cx="10710676" cy="1041400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1805,22 +1702,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>57679</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>60385</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>74057</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28899870-912B-4A41-B23D-02C58B550C88}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D210249-E8C8-4C1E-EE23-D08972AFBDB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1836,8 +1733,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1104900"/>
-          <a:ext cx="3791479" cy="428685"/>
+          <a:off x="647700" y="1682750"/>
+          <a:ext cx="10475357" cy="1727200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1854,22 +1751,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>222251</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>25401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>14279</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>111628</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF989957-03A5-40B4-A5C0-003203422C4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{833111A3-2E0A-B35C-797B-006E8D9513C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1885,8 +1782,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="755650" y="736601"/>
-          <a:ext cx="9767879" cy="1530350"/>
+          <a:off x="977901" y="1866901"/>
+          <a:ext cx="9033377" cy="1924049"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1903,22 +1800,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>33429</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>77487</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>136673</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97CBED9E-EB7C-426E-9E1A-8C81A3D6CE66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B38B7B8-866E-3180-5875-CCC1C6D90856}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1934,8 +1831,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685801" y="1473201"/>
-          <a:ext cx="9177428" cy="2025649"/>
+          <a:off x="685800" y="1473200"/>
+          <a:ext cx="9221487" cy="1057423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1948,37 +1845,6 @@
 </file>
 
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T06:23:00.915"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.3" units="cm"/>
-      <inkml:brushProperty name="height" value="0.6" units="cm"/>
-      <inkml:brushProperty name="color" value="#FFFC00"/>
-      <inkml:brushProperty name="tip" value="rectangle"/>
-      <inkml:brushProperty name="rasterOp" value="maskPen"/>
-      <inkml:brushProperty name="ignorePressure" value="1"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 0,'11624'284'0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -2009,33 +1875,8 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-09-15T06:23:00.917"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.3" units="cm"/>
-      <inkml:brushProperty name="height" value="0.6" units="cm"/>
-      <inkml:brushProperty name="color" value="#FFFC00"/>
-      <inkml:brushProperty name="tip" value="rectangle"/>
-      <inkml:brushProperty name="rasterOp" value="maskPen"/>
-      <inkml:brushProperty name="ignorePressure" value="1"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1,'0'0</inkml:trace>
-</inkml:ink>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2473,11 +2314,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF3FB42A-7605-4F6D-872D-72C64FCA20CF}">
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -2743,6 +2584,9 @@
       </c>
     </row>
     <row r="2" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B2" s="22">
+        <v>100170835</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>104</v>
       </c>
@@ -2899,6 +2743,9 @@
       <c r="BN2" s="1"/>
     </row>
     <row r="3" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B3" s="22">
+        <v>100170836</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>139</v>
       </c>
@@ -2942,19 +2789,19 @@
         <v>15</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>144</v>
+        <v>343</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>116</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
@@ -2967,14 +2814,14 @@
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI3" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
@@ -2986,7 +2833,7 @@
         <v>16</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AR3" s="1" t="s">
         <v>140</v>
@@ -3001,18 +2848,16 @@
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
       <c r="AX3" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>133</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BA3" s="1"/>
-      <c r="BB3" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="BB3" s="1"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="1"/>
       <c r="BE3" s="1"/>
@@ -3020,28 +2865,33 @@
       <c r="BG3" s="1"/>
       <c r="BH3" s="1"/>
       <c r="BI3" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="BJ3" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="BL3" s="1"/>
+      <c r="BL3" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="BM3" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B4" s="22">
+        <v>100170837</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>105</v>
@@ -3050,56 +2900,56 @@
         <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="S4" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V4" s="1" t="s">
         <v>116</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AE4" s="4"/>
       <c r="AF4" s="1"/>
@@ -3108,7 +2958,7 @@
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AL4" s="1"/>
       <c r="AM4" s="1"/>
@@ -3120,10 +2970,10 @@
         <v>20</v>
       </c>
       <c r="AQ4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AR4" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AS4" s="6"/>
       <c r="AT4" s="1"/>
@@ -3133,13 +2983,13 @@
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
       <c r="AX4" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AY4" s="1" t="s">
         <v>133</v>
       </c>
       <c r="AZ4" s="1" t="s">
-        <v>170</v>
+        <v>344</v>
       </c>
       <c r="BA4" s="1"/>
       <c r="BB4" s="1"/>
@@ -3150,24 +3000,29 @@
       <c r="BG4" s="3"/>
       <c r="BH4" s="3"/>
       <c r="BI4" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="BJ4" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="BL4" s="1"/>
+      <c r="BL4" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="BM4" s="1"/>
       <c r="BN4" s="1"/>
     </row>
     <row r="5" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B5" s="22">
+        <v>100170838</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>105</v>
@@ -3176,49 +3031,49 @@
         <v>106</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1" t="s">
-        <v>176</v>
+        <v>345</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>116</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -3235,10 +3090,10 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1" t="s">
@@ -3248,10 +3103,10 @@
         <v>28</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="AS5" s="6"/>
       <c r="AT5" s="1"/>
@@ -3261,13 +3116,13 @@
       <c r="AV5" s="1"/>
       <c r="AW5" s="1"/>
       <c r="AX5" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AY5" s="1" t="s">
         <v>133</v>
       </c>
       <c r="AZ5" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="BA5" s="1"/>
       <c r="BB5" s="1"/>
@@ -3278,27 +3133,38 @@
       <c r="BG5" s="3"/>
       <c r="BH5" s="3"/>
       <c r="BI5" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="BJ5" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="BK5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="BL5" s="1"/>
+      <c r="BL5" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="BM5" s="1"/>
       <c r="BN5" s="1"/>
     </row>
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B9" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AD2" r:id="rId1" xr:uid="{711B258B-3351-4824-8B14-5F781F06734D}"/>
-    <hyperlink ref="AE2" r:id="rId2" xr:uid="{E7DBDCBD-1022-442A-B9FB-D7F64F7FB265}"/>
-    <hyperlink ref="AD3" r:id="rId3" xr:uid="{E0A0CE94-E81F-4C46-A109-99B1034183F6}"/>
-    <hyperlink ref="AE3" r:id="rId4" xr:uid="{B883D88A-8742-42A2-BCBB-F5E1FBA49A94}"/>
-    <hyperlink ref="AD4" r:id="rId5" xr:uid="{FB0DBB69-F43F-4EF6-9602-CF9692B942D5}"/>
-    <hyperlink ref="AD5" r:id="rId6" xr:uid="{4AA52AC5-DF4D-401F-9525-5E8D01FFDB0E}"/>
-    <hyperlink ref="AE5" r:id="rId7" xr:uid="{291BC1E6-7241-4805-A8FB-A6755621A2EF}"/>
+    <hyperlink ref="AD2" r:id="rId1" xr:uid="{A870BFB5-79E0-4C81-8E98-E79856C373B2}"/>
+    <hyperlink ref="AE2" r:id="rId2" xr:uid="{605F3346-DC33-4C35-AE61-8393049D8D74}"/>
+    <hyperlink ref="AD3" r:id="rId3" xr:uid="{51053906-68B9-4939-992B-B0A4D35A86A6}"/>
+    <hyperlink ref="AE3" r:id="rId4" xr:uid="{B08B31F8-011C-4338-9902-77A23DF991EF}"/>
+    <hyperlink ref="AD4" r:id="rId5" xr:uid="{8A5CBA59-C5CD-42E2-82E9-9A71F52F083F}"/>
+    <hyperlink ref="AD5" r:id="rId6" xr:uid="{6C58AA18-B9EC-43B3-AD4A-456EFF020151}"/>
+    <hyperlink ref="AE5" r:id="rId7" xr:uid="{4D12F31D-C3FB-417D-BF2E-C79DDC8C827F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId8"/>
@@ -3332,10 +3198,10 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H1" t="s">
         <v>83</v>
@@ -3360,7 +3226,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3" s="12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C3" s="9">
         <v>7000</v>
@@ -3372,10 +3238,10 @@
         <v>34</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3386,7 +3252,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE10426-318E-4B81-9E2B-48E44290AFBA}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
@@ -3407,16 +3273,16 @@
         <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I1" t="s">
         <v>84</v>
@@ -3438,8 +3304,8 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="7">
-        <v>100167642</v>
+      <c r="B2" s="22">
+        <v>100170835</v>
       </c>
       <c r="C2" s="8">
         <v>3900</v>
@@ -3447,7 +3313,9 @@
       <c r="D2" s="8">
         <v>3900</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" s="22">
+        <v>100170835</v>
+      </c>
       <c r="F2" s="8">
         <v>1000</v>
       </c>
@@ -3475,6 +3343,126 @@
       <c r="N2" s="8" t="s">
         <v>133</v>
       </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B3" s="22">
+        <v>100170838</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="22">
+        <v>100170838</v>
+      </c>
+      <c r="F3">
+        <v>5200</v>
+      </c>
+      <c r="G3">
+        <v>5200</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>100170831</v>
+      </c>
+      <c r="C4">
+        <v>3400</v>
+      </c>
+      <c r="D4">
+        <v>3400</v>
+      </c>
+      <c r="E4">
+        <v>100170831</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3493,49 +3481,49 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" t="s">
         <v>194</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>195</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>196</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>197</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>198</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>199</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>200</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>201</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>202</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>203</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>204</v>
-      </c>
-      <c r="L1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M1" t="s">
-        <v>206</v>
-      </c>
-      <c r="N1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.35">
@@ -3549,7 +3537,7 @@
         <v>133</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M2" s="13">
         <v>2</v>
@@ -3563,15 +3551,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E30F7F34-1B02-49D6-BF8D-3702A21D16C7}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B1" t="s">
         <v>39</v>
@@ -3583,29 +3571,31 @@
         <v>41</v>
       </c>
       <c r="E1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1" t="s">
         <v>211</v>
       </c>
-      <c r="F1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G1" t="s">
-        <v>213</v>
-      </c>
-      <c r="H1" t="s">
-        <v>214</v>
-      </c>
-      <c r="I1" t="s">
-        <v>215</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B2" s="7">
-        <v>362243</v>
+        <v>100170831</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>133</v>
       </c>
@@ -3622,9 +3612,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B3" s="7">
-        <v>900100545</v>
+        <v>100170832</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>139</v>
@@ -3641,41 +3631,28 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1</v>
-      </c>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" s="15" t="s">
-        <v>217</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-    </row>
+    <row r="19" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3684,7 +3661,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0466353-6ED0-44E0-BF80-9A738EBFEE6B}">
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BM7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
@@ -3693,7 +3670,7 @@
   <sheetData>
     <row r="1" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
         <v>39</v>
@@ -3702,195 +3679,195 @@
         <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E1" t="s">
         <v>95</v>
       </c>
       <c r="F1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K1" t="s">
+        <v>220</v>
+      </c>
+      <c r="L1" t="s">
+        <v>221</v>
+      </c>
+      <c r="M1" t="s">
         <v>222</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>223</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>224</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>225</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>226</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>227</v>
       </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
         <v>228</v>
       </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
         <v>229</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>230</v>
       </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
         <v>231</v>
       </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
         <v>232</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="X1" t="s">
         <v>233</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
         <v>234</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
         <v>235</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
         <v>236</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>237</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AC1" t="s">
         <v>238</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AD1" t="s">
         <v>239</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AE1" t="s">
         <v>240</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AF1" t="s">
         <v>241</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AG1" t="s">
         <v>242</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AH1" t="s">
         <v>243</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AI1" t="s">
         <v>244</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AJ1" t="s">
         <v>245</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AK1" t="s">
         <v>246</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AL1" t="s">
         <v>247</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AM1" t="s">
         <v>248</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AN1" t="s">
         <v>249</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AO1" t="s">
         <v>250</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AP1" t="s">
         <v>251</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AQ1" t="s">
         <v>252</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AR1" t="s">
         <v>253</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AS1" t="s">
         <v>254</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AT1" t="s">
         <v>255</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AU1" t="s">
         <v>256</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AV1" t="s">
         <v>257</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AW1" t="s">
         <v>258</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AX1" t="s">
         <v>259</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AY1" t="s">
         <v>260</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AZ1" t="s">
         <v>261</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BA1" t="s">
         <v>262</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BB1" t="s">
         <v>263</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BC1" t="s">
         <v>264</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BD1" t="s">
         <v>265</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BE1" t="s">
         <v>266</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BF1" t="s">
         <v>267</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BG1" t="s">
         <v>268</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BH1" t="s">
         <v>269</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BI1" t="s">
         <v>270</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BJ1" t="s">
         <v>271</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BK1" t="s">
         <v>272</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BL1" t="s">
         <v>273</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BM1" t="s">
         <v>274</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>275</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>276</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>277</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>278</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>279</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>280</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:65" x14ac:dyDescent="0.35">
-      <c r="B2" s="7">
-        <v>700000801</v>
+      <c r="B2" s="22">
+        <v>100170835</v>
       </c>
       <c r="C2" s="16">
         <v>1000</v>
@@ -3902,13 +3879,22 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G2" t="s">
-        <v>283</v>
+        <v>276</v>
+      </c>
+      <c r="H2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I2" t="s">
+        <v>306</v>
       </c>
       <c r="L2" t="s">
-        <v>284</v>
+        <v>277</v>
+      </c>
+      <c r="M2" t="s">
+        <v>307</v>
       </c>
       <c r="R2" t="s">
         <v>133</v>
@@ -3916,41 +3902,17 @@
       <c r="S2" t="s">
         <v>133</v>
       </c>
-      <c r="T2" t="s">
-        <v>133</v>
-      </c>
-      <c r="U2" t="s">
-        <v>133</v>
-      </c>
-      <c r="V2" t="s">
-        <v>133</v>
-      </c>
-      <c r="W2" t="s">
-        <v>133</v>
-      </c>
       <c r="X2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="Y2" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AJ2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AK2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AP2">
         <v>50</v>
@@ -3959,23 +3921,74 @@
         <v>50</v>
       </c>
       <c r="AV2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AW2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="BB2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="BC2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="BH2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="BI2" t="s">
-        <v>289</v>
-      </c>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="B3" s="22">
+        <v>100170831</v>
+      </c>
+      <c r="C3" s="16">
+        <v>3900</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G3" t="s">
+        <v>349</v>
+      </c>
+      <c r="H3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I3" t="s">
+        <v>306</v>
+      </c>
+      <c r="L3" t="s">
+        <v>350</v>
+      </c>
+      <c r="M3" t="s">
+        <v>307</v>
+      </c>
+      <c r="R3" t="s">
+        <v>133</v>
+      </c>
+      <c r="S3" t="s">
+        <v>133</v>
+      </c>
+      <c r="X3" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3985,7 +3998,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6DBB7C-1AA2-464D-8112-57DE663CFA87}">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -3993,88 +4006,88 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B1" t="s">
         <v>106</v>
       </c>
       <c r="C1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1" t="s">
         <v>291</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>292</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>293</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>294</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>295</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>296</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>297</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>298</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>299</v>
       </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
         <v>300</v>
       </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
         <v>301</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>302</v>
-      </c>
-      <c r="O1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>305</v>
-      </c>
-      <c r="R1" t="s">
-        <v>306</v>
-      </c>
-      <c r="S1" t="s">
-        <v>307</v>
-      </c>
-      <c r="T1" t="s">
-        <v>308</v>
-      </c>
-      <c r="U1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
-        <v>100168037</v>
+      <c r="A2" s="22">
+        <v>100170831</v>
       </c>
       <c r="B2" s="17">
-        <v>1000</v>
+        <v>3900</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="17">
-        <v>1000</v>
+        <v>3900</v>
       </c>
       <c r="E2" s="17">
-        <v>1000</v>
+        <v>3900</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="H2" s="9">
         <v>100</v>
@@ -4083,28 +4096,28 @@
         <v>100</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="R2" s="9">
         <v>5000000</v>
@@ -4113,11 +4126,82 @@
         <v>5000000</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>316</v>
-      </c>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="22">
+        <v>100170835</v>
+      </c>
+      <c r="B3" s="17">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="H3" s="9">
+        <v>100</v>
+      </c>
+      <c r="I3" s="9">
+        <v>100</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="R3" s="9">
+        <v>5000000</v>
+      </c>
+      <c r="S3" s="9">
+        <v>5000000</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B8" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4127,7 +4211,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5109CCA9-7A08-4BF5-93D5-CC72B1946166}">
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
@@ -4145,105 +4229,105 @@
         <v>41</v>
       </c>
       <c r="D1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K1" t="s">
         <v>317</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>318</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>319</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>320</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>321</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>322</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>323</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>324</v>
       </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
         <v>325</v>
       </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
         <v>326</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>327</v>
       </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
         <v>328</v>
       </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
         <v>329</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="X1" t="s">
         <v>330</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
         <v>331</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
         <v>332</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
         <v>333</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>334</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AC1" t="s">
         <v>335</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AD1" t="s">
         <v>336</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AE1" t="s">
         <v>337</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AF1" t="s">
         <v>338</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AG1" t="s">
         <v>339</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AH1" t="s">
         <v>340</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AI1" t="s">
         <v>341</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>342</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>343</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>344</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>345</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>346</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>347</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
-        <v>700000800</v>
+        <v>100170831</v>
       </c>
       <c r="B2" s="19">
         <v>1000</v>
@@ -4258,7 +4342,7 @@
         <v>133</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -4270,13 +4354,13 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
       <c r="P2" s="21"/>
-      <c r="Q2">
-        <v>100098685</v>
+      <c r="Q2" s="7">
+        <v>100170835</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
-        <v>100168036</v>
+      <c r="A3" s="24">
+        <v>100170835</v>
       </c>
       <c r="B3" s="19">
         <v>1000</v>
@@ -4290,121 +4374,76 @@
       <c r="E3" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="21"/>
-      <c r="Q3">
-        <v>100098685</v>
+      <c r="F3" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="24">
+        <v>100170831</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
-        <v>100168037</v>
-      </c>
-      <c r="B4" s="19">
-        <v>1000</v>
-      </c>
-      <c r="C4" s="19">
-        <v>1000</v>
-      </c>
-      <c r="D4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="21"/>
-      <c r="Q4">
-        <v>100098685</v>
-      </c>
+      <c r="A4" s="27"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A5" s="7">
-        <v>700000799</v>
-      </c>
-      <c r="B5" s="19">
-        <v>1000</v>
-      </c>
-      <c r="C5" s="19">
-        <v>1000</v>
-      </c>
-      <c r="D5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="21"/>
-      <c r="Q5">
-        <v>100098685</v>
-      </c>
+      <c r="A5" s="27"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
-        <v>900100545</v>
-      </c>
-      <c r="B6" s="19">
-        <v>1000</v>
-      </c>
-      <c r="C6" s="19">
-        <v>1000</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="21"/>
-      <c r="Q6">
-        <v>100098685</v>
-      </c>
+      <c r="A6" s="27"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
